--- a/data/trans_camb/P29A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 11,21</t>
+          <t>-2,01; 10,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 11,14</t>
+          <t>-1,82; 11,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -1,92</t>
+          <t>-20,91; -1,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 9,59</t>
+          <t>-3,65; 9,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 12,02</t>
+          <t>-1,29; 11,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 3,66</t>
+          <t>-12,34; 4,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 7,8</t>
+          <t>-1,05; 8,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 9,57</t>
+          <t>0,02; 9,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,98; -1,02</t>
+          <t>-13,25; -0,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 22,29</t>
+          <t>-3,39; 21,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 22,04</t>
+          <t>-3,27; 22,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,38; -3,86</t>
+          <t>-37,56; -2,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 29,67</t>
+          <t>-9,49; 27,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 36,13</t>
+          <t>-3,28; 34,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 10,23</t>
+          <t>-32,08; 12,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 18,04</t>
+          <t>-2,28; 18,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 22,04</t>
+          <t>0,05; 22,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,59; -1,54</t>
+          <t>-28,73; -1,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,1</t>
+          <t>-7,44; 3,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,25; -0,32</t>
+          <t>-11,39; -0,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -4,74</t>
+          <t>-17,93; -3,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 3,55</t>
+          <t>-7,03; 3,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,0</t>
+          <t>0,88; 11,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 1,75</t>
+          <t>-16,51; 2,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,34</t>
+          <t>-6,94; 1,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 2,87</t>
+          <t>-4,85; 3,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,74; -5,15</t>
+          <t>-21,4; -5,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 4,94</t>
+          <t>-11,07; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,46; -0,48</t>
+          <t>-16,87; -0,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,78; -7,4</t>
+          <t>-26,81; -5,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 12,08</t>
+          <t>-20,34; 11,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 39,45</t>
+          <t>2,52; 39,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 5,04</t>
+          <t>-46,53; 6,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 2,52</t>
+          <t>-13,21; 2,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 5,85</t>
+          <t>-9,39; 6,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,29; -10,38</t>
+          <t>-41,31; -10,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,09</t>
+          <t>-5,43; 5,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 8,67</t>
+          <t>-2,32; 8,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,37; -1,31</t>
+          <t>-13,83; -1,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 3,97</t>
+          <t>-6,39; 4,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 11,07</t>
+          <t>0,31; 10,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 2,59</t>
+          <t>-7,65; 2,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 3,78</t>
+          <t>-4,67; 3,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,11</t>
+          <t>0,72; 9,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; -0,07</t>
+          <t>-8,35; -0,22</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 8,82</t>
+          <t>-8,7; 10,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 15,33</t>
+          <t>-3,79; 15,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,2; -2,08</t>
+          <t>-22,02; -3,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 14,68</t>
+          <t>-19,44; 15,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 40,33</t>
+          <t>1,36; 37,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 9,13</t>
+          <t>-23,25; 7,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 9,1</t>
+          <t>-10,09; 7,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 21,57</t>
+          <t>1,49; 21,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,53; -0,29</t>
+          <t>-18,19; -0,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 8,1</t>
+          <t>-3,51; 8,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 6,87</t>
+          <t>-5,22; 6,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-41,44; -2,29</t>
+          <t>-40,49; -3,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 11,16</t>
+          <t>-0,17; 11,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 18,66</t>
+          <t>7,14; 18,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 6,75</t>
+          <t>-3,91; 6,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 8,17</t>
+          <t>-0,7; 8,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,03</t>
+          <t>2,34; 11,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -0,95</t>
+          <t>-22,06; -0,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 14,65</t>
+          <t>-5,82; 15,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 12,41</t>
+          <t>-8,49; 11,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,02; -4,0</t>
+          <t>-66,78; -5,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 48,79</t>
+          <t>-0,7; 49,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,99; 83,2</t>
+          <t>24,73; 82,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 28,58</t>
+          <t>-14,1; 30,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 20,72</t>
+          <t>-1,65; 20,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,13; 27,56</t>
+          <t>5,21; 27,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,37; -2,26</t>
+          <t>-53,2; -1,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 13,26</t>
+          <t>-1,79; 12,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,71; 20,48</t>
+          <t>6,68; 20,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 8,93</t>
+          <t>-3,74; 9,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 10,06</t>
+          <t>-1,16; 10,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 12,99</t>
+          <t>1,69; 13,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 12,06</t>
+          <t>2,8; 11,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 9,67</t>
+          <t>0,3; 9,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 15,54</t>
+          <t>5,85; 15,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,9</t>
+          <t>1,64; 10,15</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 32,58</t>
+          <t>-3,23; 31,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14,48; 50,89</t>
+          <t>14,1; 52,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 22,5</t>
+          <t>-7,78; 22,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 68,87</t>
+          <t>-7,0; 70,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,81; 89,92</t>
+          <t>7,59; 93,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,13; 84,66</t>
+          <t>13,92; 83,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,39; 34,54</t>
+          <t>0,85; 35,07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19,36; 56,54</t>
+          <t>18,27; 53,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4,71; 34,95</t>
+          <t>5,28; 37,53</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 12,52</t>
+          <t>-3,93; 11,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 16,39</t>
+          <t>-0,15; 16,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,77</t>
+          <t>1,77; 16,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 9,29</t>
+          <t>0,14; 9,38</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,69; 14,49</t>
+          <t>4,82; 14,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,49; 70,11</t>
+          <t>9,49; 72,04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 9,3</t>
+          <t>-0,73; 9,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,9; 13,67</t>
+          <t>3,81; 13,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,45; 53,48</t>
+          <t>9,19; 50,01</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 31,83</t>
+          <t>-8,98; 30,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 41,77</t>
+          <t>0,3; 43,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4,48; 42,12</t>
+          <t>4,12; 42,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 144,09</t>
+          <t>2,3; 163,81</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>45,72; 247,26</t>
+          <t>46,16; 246,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>108,45; 1258,79</t>
+          <t>107,07; 1501,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 42,58</t>
+          <t>-2,92; 43,38</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15,08; 65,23</t>
+          <t>14,06; 63,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37,45; 245,09</t>
+          <t>36,47; 246,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 9,11</t>
+          <t>-10,58; 7,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 10,27</t>
+          <t>-6,72; 10,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 9,73</t>
+          <t>-5,58; 9,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,85</t>
+          <t>-2,91; 3,73</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,24</t>
+          <t>-0,79; 6,88</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,74</t>
+          <t>-1,42; 4,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 4,48</t>
+          <t>-4,72; 4,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,76</t>
+          <t>-1,49; 7,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 6,25</t>
+          <t>-1,6; 6,2</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,61; 32,39</t>
+          <t>-27,35; 27,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 36,39</t>
+          <t>-16,98; 35,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 35,34</t>
+          <t>-15,14; 33,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 140,04</t>
+          <t>-46,26; 131,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 238,32</t>
+          <t>-17,83; 251,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 173,44</t>
+          <t>-21,35; 164,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 32,52</t>
+          <t>-26,73; 31,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 49,94</t>
+          <t>-8,58; 54,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 49,85</t>
+          <t>-8,91; 47,36</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,64</t>
+          <t>-1,45; 3,68</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,36</t>
+          <t>-0,47; 4,6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -4,75</t>
+          <t>-20,69; -4,75</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,27</t>
+          <t>-0,99; 3,2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,28</t>
+          <t>4,07; 8,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 16,42</t>
+          <t>-1,57; 16,54</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,7</t>
+          <t>-0,72; 2,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,8</t>
+          <t>2,34; 5,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 3,74</t>
+          <t>-6,39; 3,24</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 6,76</t>
+          <t>-2,6; 6,85</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,11</t>
+          <t>-0,84; 8,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-34,03; -8,72</t>
+          <t>-37,37; -8,77</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 13,86</t>
+          <t>-3,95; 13,41</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,98; 35,07</t>
+          <t>16,05; 35,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 67,86</t>
+          <t>-6,29; 66,32</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,94</t>
+          <t>-1,81; 7,22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,1</t>
+          <t>5,77; 14,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 9,37</t>
+          <t>-16,09; 8,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P29A_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,54</t>
+          <t>-13,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,2</t>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,48</t>
+          <t>-9,21</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,9</t>
+          <t>-2,47; 10,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 11,18</t>
+          <t>-2,8; 11,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,91; -1,24</t>
+          <t>-20,8; -3,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 9,06</t>
+          <t>-3,91; 9,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 11,43</t>
+          <t>-1,6; 11,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 4,18</t>
+          <t>-12,78; 3,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,1</t>
+          <t>-1,27; 8,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 9,63</t>
+          <t>0,24; 9,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -0,54</t>
+          <t>-15,61; -3,74</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-21,37%</t>
+          <t>-24,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-11,55%</t>
+          <t>-14,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-16,45%</t>
+          <t>-20,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 21,44</t>
+          <t>-4,18; 20,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 22,01</t>
+          <t>-4,81; 22,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,56; -2,04</t>
+          <t>-37,68; -6,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 27,37</t>
+          <t>-10,48; 26,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 34,03</t>
+          <t>-4,04; 33,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 12,3</t>
+          <t>-33,23; 8,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 18,59</t>
+          <t>-2,73; 18,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 22,46</t>
+          <t>0,48; 22,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-28,73; -1,33</t>
+          <t>-33,53; -8,55</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,17</t>
+          <t>-13,19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,13</t>
+          <t>-2,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,57</t>
+          <t>-9,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 3,13</t>
+          <t>-7,23; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; -0,53</t>
+          <t>-11,3; -0,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,93; -3,76</t>
+          <t>-20,18; -5,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 3,61</t>
+          <t>-7,72; 2,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 11,84</t>
+          <t>0,48; 11,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 2,2</t>
+          <t>-7,51; 4,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 1,33</t>
+          <t>-6,87; 1,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 3,31</t>
+          <t>-4,73; 3,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,4; -5,12</t>
+          <t>-14,03; -4,66</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-17,05%</t>
+          <t>-20,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-15,56%</t>
+          <t>-7,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,95%</t>
+          <t>-18,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 4,9</t>
+          <t>-10,7; 5,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -0,77</t>
+          <t>-16,79; -0,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,81; -5,87</t>
+          <t>-30,21; -9,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 11,99</t>
+          <t>-21,51; 10,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 39,09</t>
+          <t>1,08; 39,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 6,69</t>
+          <t>-21,41; 13,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 2,89</t>
+          <t>-13,23; 2,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 6,73</t>
+          <t>-8,99; 6,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,31; -10,41</t>
+          <t>-27,1; -9,65</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,29</t>
+          <t>-9,45</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,32</t>
+          <t>-5,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 5,91</t>
+          <t>-5,92; 5,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 8,62</t>
+          <t>-2,83; 8,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -1,8</t>
+          <t>-14,98; -3,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 4,15</t>
+          <t>-6,31; 3,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 10,27</t>
+          <t>0,38; 11,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 2,15</t>
+          <t>-7,73; 1,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,32</t>
+          <t>-4,79; 3,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 9,01</t>
+          <t>0,89; 8,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -0,22</t>
+          <t>-9,42; -1,88</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,17%</t>
+          <t>-15,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,85%</t>
+          <t>-9,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,7%</t>
+          <t>-12,56%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 10,45</t>
+          <t>-9,41; 9,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 15,1</t>
+          <t>-4,42; 14,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,02; -3,3</t>
+          <t>-24,27; -6,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 15,0</t>
+          <t>-19,02; 14,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 37,3</t>
+          <t>1,22; 41,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 7,65</t>
+          <t>-23,46; 6,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 7,81</t>
+          <t>-10,49; 7,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 21,1</t>
+          <t>1,93; 20,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,19; -0,84</t>
+          <t>-20,13; -4,36</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-19,41</t>
+          <t>-7,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-8,35</t>
+          <t>-2,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 8,71</t>
+          <t>-3,1; 9,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,27</t>
+          <t>-5,77; 6,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-40,49; -3,1</t>
+          <t>-12,81; -1,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 11,37</t>
+          <t>-0,38; 10,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 18,42</t>
+          <t>7,2; 17,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 6,78</t>
+          <t>-1,09; 8,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 8,21</t>
+          <t>-0,69; 8,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,0</t>
+          <t>2,02; 10,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -0,55</t>
+          <t>-6,26; 1,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-33,25%</t>
+          <t>-12,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-19,89%</t>
+          <t>-5,68%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 15,36</t>
+          <t>-5,11; 16,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 11,44</t>
+          <t>-9,44; 11,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,78; -5,11</t>
+          <t>-21,12; -2,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 49,48</t>
+          <t>-1,43; 46,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,73; 82,17</t>
+          <t>24,73; 76,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 30,11</t>
+          <t>-3,66; 37,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 20,64</t>
+          <t>-1,58; 20,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,21; 27,77</t>
+          <t>4,26; 27,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,2; -1,5</t>
+          <t>-13,93; 3,96</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>4,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 12,83</t>
+          <t>-1,23; 13,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,68; 20,82</t>
+          <t>6,75; 20,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 9,16</t>
+          <t>-4,31; 8,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 10,28</t>
+          <t>-1,0; 10,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,78</t>
+          <t>1,91; 13,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,86</t>
+          <t>2,13; 11,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 9,83</t>
+          <t>0,42; 9,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 15,04</t>
+          <t>5,56; 14,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,15</t>
+          <t>0,8; 9,06</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 31,52</t>
+          <t>-2,75; 33,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14,1; 52,79</t>
+          <t>14,04; 50,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 22,43</t>
+          <t>-9,09; 20,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 70,75</t>
+          <t>-5,75; 69,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,59; 93,71</t>
+          <t>9,98; 91,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,92; 83,87</t>
+          <t>10,8; 81,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,85; 35,07</t>
+          <t>1,41; 33,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,27; 53,86</t>
+          <t>16,95; 52,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,28; 37,53</t>
+          <t>2,37; 32,73</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,17</t>
+          <t>10,51</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>24,44</t>
+          <t>10,4</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 11,74</t>
+          <t>-3,17; 13,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 16,27</t>
+          <t>0,18; 16,51</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,05</t>
+          <t>1,65; 15,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,38</t>
+          <t>0,23; 9,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,82; 14,26</t>
+          <t>4,87; 14,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,49; 72,04</t>
+          <t>6,45; 14,12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 9,39</t>
+          <t>-0,71; 9,53</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,81; 13,43</t>
+          <t>4,22; 13,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,19; 50,01</t>
+          <t>6,15; 14,05</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>482,0%</t>
+          <t>132,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>102,78%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 30,35</t>
+          <t>-6,77; 34,64</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0,3; 43,24</t>
+          <t>0,26; 42,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4,12; 42,32</t>
+          <t>3,36; 41,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,3; 163,81</t>
+          <t>0,43; 159,34</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>46,16; 246,1</t>
+          <t>46,13; 248,22</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>107,07; 1501,13</t>
+          <t>57,51; 236,92</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 43,38</t>
+          <t>-3,21; 42,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14,06; 63,22</t>
+          <t>15,01; 62,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36,47; 246,77</t>
+          <t>23,11; 67,44</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 7,95</t>
+          <t>-9,87; 8,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 10,38</t>
+          <t>-5,7; 9,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 9,64</t>
+          <t>-6,38; 8,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,73</t>
+          <t>-3,12; 3,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,88</t>
+          <t>-0,65; 7,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,55</t>
+          <t>-1,41; 5,11</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,23</t>
+          <t>-4,63; 4,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 7,34</t>
+          <t>-1,49; 7,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,2</t>
+          <t>-1,55; 6,4</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 27,89</t>
+          <t>-26,75; 30,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 35,47</t>
+          <t>-15,63; 34,37</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 33,62</t>
+          <t>-17,04; 30,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 131,91</t>
+          <t>-49,16; 139,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 251,14</t>
+          <t>-15,69; 258,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 164,98</t>
+          <t>-20,89; 178,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 31,86</t>
+          <t>-25,23; 31,73</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 54,97</t>
+          <t>-8,34; 55,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 47,36</t>
+          <t>-8,33; 49,53</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-9,18</t>
+          <t>-7,21</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,72</t>
+          <t>-3,71</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,68</t>
+          <t>-1,62; 3,62</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,6</t>
+          <t>-0,44; 4,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -4,75</t>
+          <t>-10,0; -4,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,2</t>
+          <t>-1,1; 3,17</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,4</t>
+          <t>3,84; 8,2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 16,54</t>
+          <t>-2,2; 1,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,77</t>
+          <t>-0,83; 2,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,71</t>
+          <t>2,39; 5,88</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 3,24</t>
+          <t>-5,42; -1,96</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-16,7%</t>
+          <t>-13,13%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>-0,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-6,91%</t>
+          <t>-9,42%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,85</t>
+          <t>-2,8; 6,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,57</t>
+          <t>-0,76; 8,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,37; -8,77</t>
+          <t>-17,8; -8,74</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 13,41</t>
+          <t>-4,23; 13,53</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>16,05; 35,4</t>
+          <t>14,98; 35,18</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 66,32</t>
+          <t>-8,6; 8,25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,22</t>
+          <t>-2,1; 6,75</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>5,77; 14,83</t>
+          <t>5,89; 15,22</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 8,3</t>
+          <t>-13,38; -5,08</t>
         </is>
       </c>
     </row>
